--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/148.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/148.xlsx
@@ -426,13 +426,13 @@
         <v>0.7317177650699328</v>
       </c>
       <c r="E2">
-        <v>-13.10142532625287</v>
+        <v>-18.32415062709116</v>
       </c>
       <c r="F2">
-        <v>-1.814581189817368</v>
+        <v>-3.307855084189355</v>
       </c>
       <c r="G2">
-        <v>-7.31929290453408</v>
+        <v>-10.94126477323005</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>0.4558982724826072</v>
       </c>
       <c r="E3">
-        <v>-13.93589628859431</v>
+        <v>-18.01174026225</v>
       </c>
       <c r="F3">
-        <v>-2.097190326426058</v>
+        <v>-3.098108315963506</v>
       </c>
       <c r="G3">
-        <v>-5.897598985967305</v>
+        <v>-10.84643088571208</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.006797198311748497</v>
       </c>
       <c r="E4">
-        <v>-13.00468806450102</v>
+        <v>-18.06184329867086</v>
       </c>
       <c r="F4">
-        <v>-2.417228415762842</v>
+        <v>-2.873252954677997</v>
       </c>
       <c r="G4">
-        <v>-5.992634816763162</v>
+        <v>-10.2264087432986</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.6088781702661532</v>
       </c>
       <c r="E5">
-        <v>-15.19559548872999</v>
+        <v>-19.14932463229484</v>
       </c>
       <c r="F5">
-        <v>-2.120868380267679</v>
+        <v>-2.818111850143246</v>
       </c>
       <c r="G5">
-        <v>-6.793634552171983</v>
+        <v>-10.35361976619064</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.319332259753896</v>
       </c>
       <c r="E6">
-        <v>-16.00181783021158</v>
+        <v>-19.47753937142278</v>
       </c>
       <c r="F6">
-        <v>-2.665678994149692</v>
+        <v>-2.979766920432166</v>
       </c>
       <c r="G6">
-        <v>-7.220019575447955</v>
+        <v>-9.719501320870936</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.085289308463799</v>
       </c>
       <c r="E7">
-        <v>-15.80943919741772</v>
+        <v>-20.40443648826076</v>
       </c>
       <c r="F7">
-        <v>-2.029477918186421</v>
+        <v>-2.953008168219534</v>
       </c>
       <c r="G7">
-        <v>-6.415007458845538</v>
+        <v>-10.75811877290649</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.862422867279567</v>
       </c>
       <c r="E8">
-        <v>-17.49976910483882</v>
+        <v>-22.01774158128539</v>
       </c>
       <c r="F8">
-        <v>-2.219503743653822</v>
+        <v>-2.766789519335399</v>
       </c>
       <c r="G8">
-        <v>-5.657309659090384</v>
+        <v>-10.32937995175209</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.595926831277128</v>
       </c>
       <c r="E9">
-        <v>-19.12378856736559</v>
+        <v>-22.32653369539442</v>
       </c>
       <c r="F9">
-        <v>-2.060542524158805</v>
+        <v>-2.904395427186245</v>
       </c>
       <c r="G9">
-        <v>-5.403033277310042</v>
+        <v>-10.40761807448169</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.240273871178919</v>
       </c>
       <c r="E10">
-        <v>-19.04701734751356</v>
+        <v>-22.9024423773199</v>
       </c>
       <c r="F10">
-        <v>-1.990714465572418</v>
+        <v>-2.678548510119585</v>
       </c>
       <c r="G10">
-        <v>-5.880427186255105</v>
+        <v>-10.48513118773818</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.755111769383641</v>
       </c>
       <c r="E11">
-        <v>-20.95618123288131</v>
+        <v>-23.60938698313133</v>
       </c>
       <c r="F11">
-        <v>-1.696731016155888</v>
+        <v>-2.409141893176713</v>
       </c>
       <c r="G11">
-        <v>-4.902922404874501</v>
+        <v>-9.877722223829325</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.10970584445909</v>
       </c>
       <c r="E12">
-        <v>-21.54780824808741</v>
+        <v>-24.52729055059008</v>
       </c>
       <c r="F12">
-        <v>-2.162616440633969</v>
+        <v>-2.541409801483918</v>
       </c>
       <c r="G12">
-        <v>-5.812660319066223</v>
+        <v>-9.041289719513685</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.286055958485345</v>
       </c>
       <c r="E13">
-        <v>-21.25204002522444</v>
+        <v>-25.88524857974419</v>
       </c>
       <c r="F13">
-        <v>-1.365741909754095</v>
+        <v>-2.289756754717845</v>
       </c>
       <c r="G13">
-        <v>-4.657965208787208</v>
+        <v>-8.575641626141955</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.276211975328621</v>
       </c>
       <c r="E14">
-        <v>-22.65247061209649</v>
+        <v>-25.46121585908796</v>
       </c>
       <c r="F14">
-        <v>-1.157166453035804</v>
+        <v>-2.250618051670374</v>
       </c>
       <c r="G14">
-        <v>-3.289210223938918</v>
+        <v>-8.475173190116154</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.084427408804137</v>
       </c>
       <c r="E15">
-        <v>-24.3299396533358</v>
+        <v>-27.00703310397628</v>
       </c>
       <c r="F15">
-        <v>-0.9468058645644811</v>
+        <v>-1.895311391791999</v>
       </c>
       <c r="G15">
-        <v>-5.392174687941233</v>
+        <v>-7.473124024107394</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.724266698876886</v>
       </c>
       <c r="E16">
-        <v>-26.11253269018917</v>
+        <v>-26.96290312477153</v>
       </c>
       <c r="F16">
-        <v>-0.9290059058131253</v>
+        <v>-2.107780175303447</v>
       </c>
       <c r="G16">
-        <v>-3.522292493176845</v>
+        <v>-7.769421160417704</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.219495334808682</v>
       </c>
       <c r="E17">
-        <v>-25.68902074404382</v>
+        <v>-28.50501607792157</v>
       </c>
       <c r="F17">
-        <v>-0.2515811260495372</v>
+        <v>-1.450750629364185</v>
       </c>
       <c r="G17">
-        <v>-2.568464733493109</v>
+        <v>-7.134514805259658</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.600229549860025</v>
       </c>
       <c r="E18">
-        <v>-26.47531327141765</v>
+        <v>-29.29128596292536</v>
       </c>
       <c r="F18">
-        <v>-0.6196338751547883</v>
+        <v>-1.695278059731377</v>
       </c>
       <c r="G18">
-        <v>-1.658190510924025</v>
+        <v>-7.473425283751467</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.900418790649173</v>
       </c>
       <c r="E19">
-        <v>-27.09625762734941</v>
+        <v>-29.75106192892413</v>
       </c>
       <c r="F19">
-        <v>-0.4121485499385822</v>
+        <v>-1.298282153572311</v>
       </c>
       <c r="G19">
-        <v>-3.570335130042749</v>
+        <v>-6.848831277948252</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.157386188565133</v>
       </c>
       <c r="E20">
-        <v>-28.65997140151604</v>
+        <v>-30.50959943910495</v>
       </c>
       <c r="F20">
-        <v>-0.1955934300291242</v>
+        <v>-1.383746475253942</v>
       </c>
       <c r="G20">
-        <v>-1.826405950865473</v>
+        <v>-6.388264871979304</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.401902393445953</v>
       </c>
       <c r="E21">
-        <v>-29.94738033410466</v>
+        <v>-30.90149584396574</v>
       </c>
       <c r="F21">
-        <v>0.01529897031479632</v>
+        <v>-0.8063039842734485</v>
       </c>
       <c r="G21">
-        <v>-2.420781296986222</v>
+        <v>-6.639495551863517</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6657431945190472</v>
       </c>
       <c r="E22">
-        <v>-26.73256229437138</v>
+        <v>-32.80225488157526</v>
       </c>
       <c r="F22">
-        <v>0.6508456360298555</v>
+        <v>-0.6278231152988643</v>
       </c>
       <c r="G22">
-        <v>-1.587503742569507</v>
+        <v>-6.263841328431337</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.02475506857899076</v>
       </c>
       <c r="E23">
-        <v>-28.67866947069371</v>
+        <v>-32.87673016510541</v>
       </c>
       <c r="F23">
-        <v>-0.1558881236781383</v>
+        <v>-0.3999251605428727</v>
       </c>
       <c r="G23">
-        <v>-0.009906302921833305</v>
+        <v>-6.218556375999646</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6530625698441681</v>
       </c>
       <c r="E24">
-        <v>-30.80550125195115</v>
+        <v>-33.11097680433718</v>
       </c>
       <c r="F24">
-        <v>0.4205992596869272</v>
+        <v>-0.3318739500354905</v>
       </c>
       <c r="G24">
-        <v>-0.6655863313388061</v>
+        <v>-6.487058171962236</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.198814601638386</v>
       </c>
       <c r="E25">
-        <v>-31.13744971789841</v>
+        <v>-32.57797088516037</v>
       </c>
       <c r="F25">
-        <v>0.111674547426102</v>
+        <v>-0.3161970969375099</v>
       </c>
       <c r="G25">
-        <v>-2.042200551297326</v>
+        <v>-6.436393583029229</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.651610411212979</v>
       </c>
       <c r="E26">
-        <v>-29.37538425372181</v>
+        <v>-33.15882239646522</v>
       </c>
       <c r="F26">
-        <v>0.8954161415019927</v>
+        <v>-0.4772615412682345</v>
       </c>
       <c r="G26">
-        <v>-1.392366946302706</v>
+        <v>-6.333667354945645</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.003101604155998</v>
       </c>
       <c r="E27">
-        <v>-32.24944368132591</v>
+        <v>-33.74773685574073</v>
       </c>
       <c r="F27">
-        <v>0.5500333231091555</v>
+        <v>-0.571274614546756</v>
       </c>
       <c r="G27">
-        <v>-1.426088163165723</v>
+        <v>-6.535329236470349</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.246040705338655</v>
       </c>
       <c r="E28">
-        <v>-31.87856618857171</v>
+        <v>-33.51858701400459</v>
       </c>
       <c r="F28">
-        <v>1.199122139125181</v>
+        <v>-0.3674887781514524</v>
       </c>
       <c r="G28">
-        <v>-1.406552633938483</v>
+        <v>-6.362522069865932</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.380231141793503</v>
       </c>
       <c r="E29">
-        <v>-31.71391993060083</v>
+        <v>-33.24249274646794</v>
       </c>
       <c r="F29">
-        <v>0.5249892914203181</v>
+        <v>-0.5307798740609022</v>
       </c>
       <c r="G29">
-        <v>-1.538818859868985</v>
+        <v>-6.608561814344567</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.402376482292756</v>
       </c>
       <c r="E30">
-        <v>-30.47064550569097</v>
+        <v>-33.49600804260235</v>
       </c>
       <c r="F30">
-        <v>1.098483783359069</v>
+        <v>-0.6321281406912133</v>
       </c>
       <c r="G30">
-        <v>-1.472309999985027</v>
+        <v>-6.505782617532353</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.314365623405861</v>
       </c>
       <c r="E31">
-        <v>-31.33787997747789</v>
+        <v>-32.86680375008059</v>
       </c>
       <c r="F31">
-        <v>0.9367549883712992</v>
+        <v>-0.2391398760268914</v>
       </c>
       <c r="G31">
-        <v>-2.996389160444842</v>
+        <v>-6.696877237695704</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.121822423068013</v>
       </c>
       <c r="E32">
-        <v>-29.56761344687341</v>
+        <v>-31.9368295351544</v>
       </c>
       <c r="F32">
-        <v>-0.02109369479239436</v>
+        <v>-0.4800912443161977</v>
       </c>
       <c r="G32">
-        <v>-0.7954424801167184</v>
+        <v>-6.527274679173302</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.831455637238045</v>
       </c>
       <c r="E33">
-        <v>-30.28696833570285</v>
+        <v>-32.32834781243555</v>
       </c>
       <c r="F33">
-        <v>0.9416456695174275</v>
+        <v>-0.6696333032203637</v>
       </c>
       <c r="G33">
-        <v>-1.700499282915911</v>
+        <v>-6.136233040074589</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.458033689820371</v>
       </c>
       <c r="E34">
-        <v>-29.2196953173381</v>
+        <v>-31.69325197522982</v>
       </c>
       <c r="F34">
-        <v>0.3146924872390104</v>
+        <v>-0.2733953532348594</v>
       </c>
       <c r="G34">
-        <v>-2.394863035959268</v>
+        <v>-7.0176790320877</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.013071556279047</v>
       </c>
       <c r="E35">
-        <v>-30.40083907886273</v>
+        <v>-31.69870878640907</v>
       </c>
       <c r="F35">
-        <v>0.5064214360865672</v>
+        <v>-0.2731311040333663</v>
       </c>
       <c r="G35">
-        <v>-3.547727414555066</v>
+        <v>-6.79224412304549</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.5118465848983451</v>
       </c>
       <c r="E36">
-        <v>-29.22627971854525</v>
+        <v>-31.53978425534688</v>
       </c>
       <c r="F36">
-        <v>0.7418070037964635</v>
+        <v>-0.3005359828201824</v>
       </c>
       <c r="G36">
-        <v>-2.674825940578814</v>
+        <v>-7.353795410144365</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.03046878699031067</v>
       </c>
       <c r="E37">
-        <v>-27.69341843779288</v>
+        <v>-30.82010331638888</v>
       </c>
       <c r="F37">
-        <v>0.3834378696299386</v>
+        <v>-0.6255426198389572</v>
       </c>
       <c r="G37">
-        <v>-3.616245775581362</v>
+        <v>-6.618963548428956</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.6043972596343099</v>
       </c>
       <c r="E38">
-        <v>-28.68970989032441</v>
+        <v>-30.31511733013453</v>
       </c>
       <c r="F38">
-        <v>0.6429918846839133</v>
+        <v>-0.3986826094386734</v>
       </c>
       <c r="G38">
-        <v>-2.359645452512501</v>
+        <v>-7.255929062912429</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.195027237780655</v>
       </c>
       <c r="E39">
-        <v>-28.38380241415826</v>
+        <v>-29.49883951211892</v>
       </c>
       <c r="F39">
-        <v>0.8269797401523087</v>
+        <v>-0.1780105035373019</v>
       </c>
       <c r="G39">
-        <v>-3.529655146456185</v>
+        <v>-7.014282412364407</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.790808849149921</v>
       </c>
       <c r="E40">
-        <v>-27.3450384039088</v>
+        <v>-29.10130742135557</v>
       </c>
       <c r="F40">
-        <v>1.018158653044407</v>
+        <v>-0.6376177314695656</v>
       </c>
       <c r="G40">
-        <v>-0.731860142489476</v>
+        <v>-6.47986104595986</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.381790684276881</v>
       </c>
       <c r="E41">
-        <v>-26.99146873881192</v>
+        <v>-28.40020001854003</v>
       </c>
       <c r="F41">
-        <v>0.9406052400595113</v>
+        <v>-0.5736139240922619</v>
       </c>
       <c r="G41">
-        <v>-2.684558944464272</v>
+        <v>-7.156854366558661</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.952550981482199</v>
       </c>
       <c r="E42">
-        <v>-26.13708154778475</v>
+        <v>-27.55187645420914</v>
       </c>
       <c r="F42">
-        <v>0.9359365613773333</v>
+        <v>-0.9674288994245775</v>
       </c>
       <c r="G42">
-        <v>-2.510497081100471</v>
+        <v>-7.492884670431303</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.498062858598323</v>
       </c>
       <c r="E43">
-        <v>-24.19720102322297</v>
+        <v>-28.12423934098661</v>
       </c>
       <c r="F43">
-        <v>0.5733560073349756</v>
+        <v>-0.6046727314928265</v>
       </c>
       <c r="G43">
-        <v>-1.683522805390528</v>
+        <v>-6.963700587069884</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.011753486826434</v>
       </c>
       <c r="E44">
-        <v>-24.13874295225795</v>
+        <v>-27.61705478060154</v>
       </c>
       <c r="F44">
-        <v>0.923080299285885</v>
+        <v>-0.3646267687747801</v>
       </c>
       <c r="G44">
-        <v>-2.938699593877503</v>
+        <v>-6.445692905449042</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.485148190103553</v>
       </c>
       <c r="E45">
-        <v>-23.52569172652156</v>
+        <v>-25.83186239966777</v>
       </c>
       <c r="F45">
-        <v>0.9675503749377736</v>
+        <v>-0.7218212779641353</v>
       </c>
       <c r="G45">
-        <v>-2.518869450769288</v>
+        <v>-7.084492462161271</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.921892328635866</v>
       </c>
       <c r="E46">
-        <v>-23.09022913746997</v>
+        <v>-26.61412911364878</v>
       </c>
       <c r="F46">
-        <v>1.058975628449949</v>
+        <v>-0.4113102421269491</v>
       </c>
       <c r="G46">
-        <v>-3.398034476905841</v>
+        <v>-6.388844217448677</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.321349092851865</v>
       </c>
       <c r="E47">
-        <v>-22.27815600757048</v>
+        <v>-25.18231620190356</v>
       </c>
       <c r="F47">
-        <v>0.6233380396850923</v>
+        <v>-0.5922140857547219</v>
       </c>
       <c r="G47">
-        <v>-3.403281691585585</v>
+        <v>-7.143969723319817</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.68276168845487</v>
       </c>
       <c r="E48">
-        <v>-20.01923996069431</v>
+        <v>-24.87920732267416</v>
       </c>
       <c r="F48">
-        <v>0.8035783610232227</v>
+        <v>-0.5771585082088408</v>
       </c>
       <c r="G48">
-        <v>-2.75869530127071</v>
+        <v>-6.953669634085892</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.014158429822498</v>
       </c>
       <c r="E49">
-        <v>-20.54262287260482</v>
+        <v>-23.5081212473718</v>
       </c>
       <c r="F49">
-        <v>0.2982485659260374</v>
+        <v>-0.6051241917273522</v>
       </c>
       <c r="G49">
-        <v>-3.254929524879765</v>
+        <v>-7.164018387105643</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.315993507562336</v>
       </c>
       <c r="E50">
-        <v>-19.67857644651929</v>
+        <v>-23.4636652180385</v>
       </c>
       <c r="F50">
-        <v>0.84223661097707</v>
+        <v>-0.9341028504425507</v>
       </c>
       <c r="G50">
-        <v>-2.708931180724386</v>
+        <v>-7.140553240323289</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.591493304169272</v>
       </c>
       <c r="E51">
-        <v>-19.51968587901217</v>
+        <v>-23.05756072597864</v>
       </c>
       <c r="F51">
-        <v>0.8881960912191922</v>
+        <v>-0.5295083300976049</v>
       </c>
       <c r="G51">
-        <v>-4.909761991958636</v>
+        <v>-6.895000146038927</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.849814803152646</v>
       </c>
       <c r="E52">
-        <v>-18.21143690904024</v>
+        <v>-22.63158528997312</v>
       </c>
       <c r="F52">
-        <v>0.5566933970276636</v>
+        <v>-0.483853689059713</v>
       </c>
       <c r="G52">
-        <v>-4.100436234518548</v>
+        <v>-6.343344079556934</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.087979243250342</v>
       </c>
       <c r="E53">
-        <v>-19.95756667318385</v>
+        <v>-21.35019017086668</v>
       </c>
       <c r="F53">
-        <v>0.3571546003065131</v>
+        <v>-0.6824713412289505</v>
       </c>
       <c r="G53">
-        <v>-2.982114088079505</v>
+        <v>-6.931770375343612</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.311159061185147</v>
       </c>
       <c r="E54">
-        <v>-18.59305594214063</v>
+        <v>-21.47683347496519</v>
       </c>
       <c r="F54">
-        <v>1.194690373520204</v>
+        <v>-0.9859520229185773</v>
       </c>
       <c r="G54">
-        <v>-4.024194370749132</v>
+        <v>-7.405671658744744</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.523717167932907</v>
       </c>
       <c r="E55">
-        <v>-16.89246904109217</v>
+        <v>-20.19463228748539</v>
       </c>
       <c r="F55">
-        <v>0.8162722631037223</v>
+        <v>-0.6684926413067088</v>
       </c>
       <c r="G55">
-        <v>-4.994194145392208</v>
+        <v>-7.162111512875023</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.716656960587429</v>
       </c>
       <c r="E56">
-        <v>-16.62338258708239</v>
+        <v>-20.9558234834347</v>
       </c>
       <c r="F56">
-        <v>0.923733052799291</v>
+        <v>-0.4343363708225669</v>
       </c>
       <c r="G56">
-        <v>-3.671227315897577</v>
+        <v>-7.123033833329466</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.89077045384023</v>
       </c>
       <c r="E57">
-        <v>-16.32431310666782</v>
+        <v>-19.52458115941446</v>
       </c>
       <c r="F57">
-        <v>0.5028495158456957</v>
+        <v>-0.3731664083302402</v>
       </c>
       <c r="G57">
-        <v>-3.909904407096873</v>
+        <v>-7.313787467302272</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.041507471757956</v>
       </c>
       <c r="E58">
-        <v>-16.59194139204713</v>
+        <v>-19.07922838313011</v>
       </c>
       <c r="F58">
-        <v>0.9870219791079787</v>
+        <v>-0.4302152429936394</v>
       </c>
       <c r="G58">
-        <v>-4.58282575668237</v>
+        <v>-7.771927243390933</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.157973852004718</v>
       </c>
       <c r="E59">
-        <v>-14.56954754259159</v>
+        <v>-19.85655453196875</v>
       </c>
       <c r="F59">
-        <v>0.2668923746278677</v>
+        <v>-0.5127761369284577</v>
       </c>
       <c r="G59">
-        <v>-4.961565408557151</v>
+        <v>-7.419559397281986</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.240629615730571</v>
       </c>
       <c r="E60">
-        <v>-14.5618174374605</v>
+        <v>-18.97849247882949</v>
       </c>
       <c r="F60">
-        <v>1.537273310091578</v>
+        <v>-0.6478638078747927</v>
       </c>
       <c r="G60">
-        <v>-3.980730218364041</v>
+        <v>-8.371473661644023</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.28137486131256</v>
       </c>
       <c r="E61">
-        <v>-16.16201259823292</v>
+        <v>-18.32459894601792</v>
       </c>
       <c r="F61">
-        <v>0.8840824186968899</v>
+        <v>-0.488567927949045</v>
       </c>
       <c r="G61">
-        <v>-4.478920974386805</v>
+        <v>-8.07492161332719</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.271985919728753</v>
       </c>
       <c r="E62">
-        <v>-15.34621706269912</v>
+        <v>-18.35373967625728</v>
       </c>
       <c r="F62">
-        <v>0.7062841244622123</v>
+        <v>-0.2215047623886928</v>
       </c>
       <c r="G62">
-        <v>-4.877616594772312</v>
+        <v>-8.802910577412923</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.214518757488179</v>
       </c>
       <c r="E63">
-        <v>-13.89342373087637</v>
+        <v>-18.65734668762753</v>
       </c>
       <c r="F63">
-        <v>0.4862390926847601</v>
+        <v>-0.5880772189451412</v>
       </c>
       <c r="G63">
-        <v>-6.089782775613076</v>
+        <v>-8.873703283224698</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.099429020285266</v>
       </c>
       <c r="E64">
-        <v>-14.9937478167861</v>
+        <v>-18.19598575572607</v>
       </c>
       <c r="F64">
-        <v>0.2808106037297051</v>
+        <v>-0.6720024339923703</v>
       </c>
       <c r="G64">
-        <v>-4.758764699366937</v>
+        <v>-8.462377931606872</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.922902114540626</v>
       </c>
       <c r="E65">
-        <v>-13.70539696160388</v>
+        <v>-17.62179789392351</v>
       </c>
       <c r="F65">
-        <v>0.505013211501808</v>
+        <v>-1.063595727950378</v>
       </c>
       <c r="G65">
-        <v>-4.598067508345174</v>
+        <v>-8.007422900326988</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.686587846300935</v>
       </c>
       <c r="E66">
-        <v>-14.73727316288768</v>
+        <v>-18.28209468898192</v>
       </c>
       <c r="F66">
-        <v>0.4523157908053147</v>
+        <v>-0.900515865728642</v>
       </c>
       <c r="G66">
-        <v>-5.253264197113414</v>
+        <v>-8.239723880817648</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.38260158207843</v>
       </c>
       <c r="E67">
-        <v>-13.82222253405376</v>
+        <v>-17.66208319869574</v>
       </c>
       <c r="F67">
-        <v>0.7797594847231256</v>
+        <v>-0.9261472099060643</v>
       </c>
       <c r="G67">
-        <v>-4.405642048875037</v>
+        <v>-8.433437142502562</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.010842793128941</v>
       </c>
       <c r="E68">
-        <v>-12.38695892511471</v>
+        <v>-17.78603206075969</v>
       </c>
       <c r="F68">
-        <v>0.7360349397337566</v>
+        <v>-0.8978833141225451</v>
       </c>
       <c r="G68">
-        <v>-5.360731126409235</v>
+        <v>-7.763574736995352</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.572932330910715</v>
       </c>
       <c r="E69">
-        <v>-13.91947604184249</v>
+        <v>-17.86008619620712</v>
       </c>
       <c r="F69">
-        <v>0.784885422211649</v>
+        <v>-0.8139812933625944</v>
       </c>
       <c r="G69">
-        <v>-5.099244376444362</v>
+        <v>-8.582557355773494</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.064784124383467</v>
       </c>
       <c r="E70">
-        <v>-13.96379621695556</v>
+        <v>-17.08939879026373</v>
       </c>
       <c r="F70">
-        <v>0.6467311351401502</v>
+        <v>-1.101404072948953</v>
       </c>
       <c r="G70">
-        <v>-5.725725393204962</v>
+        <v>-8.856130907502246</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.493625486218203</v>
       </c>
       <c r="E71">
-        <v>-11.06812238291285</v>
+        <v>-17.40780938316506</v>
       </c>
       <c r="F71">
-        <v>0.2130816281420119</v>
+        <v>-1.135391159118414</v>
       </c>
       <c r="G71">
-        <v>-4.506663346005897</v>
+        <v>-8.149677042149472</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.86694233075451</v>
       </c>
       <c r="E72">
-        <v>-12.74747979781336</v>
+        <v>-17.08863800663044</v>
       </c>
       <c r="F72">
-        <v>-0.4259847706675423</v>
+        <v>-1.039187054059488</v>
       </c>
       <c r="G72">
-        <v>-4.090822410272504</v>
+        <v>-8.111698463722952</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.188082267103413</v>
       </c>
       <c r="E73">
-        <v>-12.05542481453915</v>
+        <v>-17.73040428604947</v>
       </c>
       <c r="F73">
-        <v>0.4006720534451823</v>
+        <v>-1.258482413337406</v>
       </c>
       <c r="G73">
-        <v>-4.722146755157059</v>
+        <v>-8.634741485109025</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.475071670735804</v>
       </c>
       <c r="E74">
-        <v>-14.24611487201576</v>
+        <v>-17.11497108298504</v>
       </c>
       <c r="F74">
-        <v>0.008760666404499819</v>
+        <v>-1.521349069635176</v>
       </c>
       <c r="G74">
-        <v>-5.078050263901947</v>
+        <v>-7.750825826123618</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.741149533497482</v>
       </c>
       <c r="E75">
-        <v>-14.83360739045285</v>
+        <v>-17.5161168960065</v>
       </c>
       <c r="F75">
-        <v>-0.2433628930463633</v>
+        <v>-1.270740594164033</v>
       </c>
       <c r="G75">
-        <v>-3.37778055929658</v>
+        <v>-7.500700868449523</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.996899883552167</v>
       </c>
       <c r="E76">
-        <v>-12.87080825893825</v>
+        <v>-17.87379388702834</v>
       </c>
       <c r="F76">
-        <v>-0.2122552119690335</v>
+        <v>-1.453410517094575</v>
       </c>
       <c r="G76">
-        <v>-4.156149405398942</v>
+        <v>-7.498539082212379</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.260786630402718</v>
       </c>
       <c r="E77">
-        <v>-13.62244437473138</v>
+        <v>-17.81351536951224</v>
       </c>
       <c r="F77">
-        <v>-0.755243417564887</v>
+        <v>-1.606361931082281</v>
       </c>
       <c r="G77">
-        <v>-3.351666976082808</v>
+        <v>-8.027213341560753</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.542594812424213</v>
       </c>
       <c r="E78">
-        <v>-13.52770869849092</v>
+        <v>-17.87479467978404</v>
       </c>
       <c r="F78">
-        <v>-0.5311178479612444</v>
+        <v>-2.048431792729876</v>
       </c>
       <c r="G78">
-        <v>-4.67508403977078</v>
+        <v>-7.49948589823661</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.1483655289346036</v>
       </c>
       <c r="E79">
-        <v>-14.75588971953322</v>
+        <v>-18.38110524468563</v>
       </c>
       <c r="F79">
-        <v>-0.2060010380778972</v>
+        <v>-1.927531570291289</v>
       </c>
       <c r="G79">
-        <v>-2.595197388722724</v>
+        <v>-6.228921694083104</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.8010619284119583</v>
       </c>
       <c r="E80">
-        <v>-14.83398325379549</v>
+        <v>-18.69910374645226</v>
       </c>
       <c r="F80">
-        <v>-0.7308148628563296</v>
+        <v>-1.85006596425109</v>
       </c>
       <c r="G80">
-        <v>-3.182286224111537</v>
+        <v>-6.957890579648462</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.414420565058264</v>
       </c>
       <c r="E81">
-        <v>-14.5362542016872</v>
+        <v>-19.92735269460467</v>
       </c>
       <c r="F81">
-        <v>-0.6780486876654038</v>
+        <v>-2.057660633964466</v>
       </c>
       <c r="G81">
-        <v>-2.799319005583107</v>
+        <v>-6.387039970129774</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.984209609603043</v>
       </c>
       <c r="E82">
-        <v>-15.4579073456243</v>
+        <v>-20.82229689884453</v>
       </c>
       <c r="F82">
-        <v>-0.9563834484756489</v>
+        <v>-2.119469267724351</v>
       </c>
       <c r="G82">
-        <v>-2.710189188029309</v>
+        <v>-6.347326665840678</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.506306326551268</v>
       </c>
       <c r="E83">
-        <v>-16.13954231020686</v>
+        <v>-21.13260605174614</v>
       </c>
       <c r="F83">
-        <v>-1.450826839165243</v>
+        <v>-2.100142627849635</v>
       </c>
       <c r="G83">
-        <v>-1.988844488840892</v>
+        <v>-5.941685520913778</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.985016394352074</v>
       </c>
       <c r="E84">
-        <v>-17.81588376141825</v>
+        <v>-21.51711877973743</v>
       </c>
       <c r="F84">
-        <v>-0.9622574017289003</v>
+        <v>-2.462656912499769</v>
       </c>
       <c r="G84">
-        <v>-2.584689717181078</v>
+        <v>-6.48181426782803</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.416163126533184</v>
       </c>
       <c r="E85">
-        <v>-19.12519239430797</v>
+        <v>-22.49695828619909</v>
       </c>
       <c r="F85">
-        <v>-1.293311949155514</v>
+        <v>-2.348000095176081</v>
       </c>
       <c r="G85">
-        <v>-1.573049900745049</v>
+        <v>-6.46146434439813</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.795645207448101</v>
       </c>
       <c r="E86">
-        <v>-18.70092872147735</v>
+        <v>-24.13619342139163</v>
       </c>
       <c r="F86">
-        <v>-1.342913760867746</v>
+        <v>-2.074098756705619</v>
       </c>
       <c r="G86">
-        <v>-2.515433104499524</v>
+        <v>-6.022340341887043</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.120343249057309</v>
       </c>
       <c r="E87">
-        <v>-20.66508639519425</v>
+        <v>-24.48051594256485</v>
       </c>
       <c r="F87">
-        <v>-2.474204354094794</v>
+        <v>-2.416654357152701</v>
       </c>
       <c r="G87">
-        <v>-1.888051619352242</v>
+        <v>-5.76447863928767</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.381037297595438</v>
       </c>
       <c r="E88">
-        <v>-21.07039840430277</v>
+        <v>-24.7339972751442</v>
       </c>
       <c r="F88">
-        <v>-1.865716309592181</v>
+        <v>-2.254846038894263</v>
       </c>
       <c r="G88">
-        <v>-1.857293340746873</v>
+        <v>-6.492742378653164</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.568447015744754</v>
       </c>
       <c r="E89">
-        <v>-23.35524449334686</v>
+        <v>-26.81153435259114</v>
       </c>
       <c r="F89">
-        <v>-2.022902337742999</v>
+        <v>-2.922047936539902</v>
       </c>
       <c r="G89">
-        <v>-1.631533998241814</v>
+        <v>-5.717991958825224</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.673876471548704</v>
       </c>
       <c r="E90">
-        <v>-24.08857198872697</v>
+        <v>-26.92612285888123</v>
       </c>
       <c r="F90">
-        <v>-2.863194917673206</v>
+        <v>-2.90822579805679</v>
       </c>
       <c r="G90">
-        <v>-2.654254210597783</v>
+        <v>-6.748879287026575</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.688242597801228</v>
       </c>
       <c r="E91">
-        <v>-26.92199289058624</v>
+        <v>-28.41604967756688</v>
       </c>
       <c r="F91">
-        <v>-2.698425185949759</v>
+        <v>-3.145230824039159</v>
       </c>
       <c r="G91">
-        <v>-2.824823448417652</v>
+        <v>-6.741169026465613</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.603844518846712</v>
       </c>
       <c r="E92">
-        <v>-28.24798442172021</v>
+        <v>-29.88268202595707</v>
       </c>
       <c r="F92">
-        <v>-2.644108306980792</v>
+        <v>-3.097824185944346</v>
       </c>
       <c r="G92">
-        <v>-2.624386468742478</v>
+        <v>-6.453601798742361</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.417277510111869</v>
       </c>
       <c r="E93">
-        <v>-30.60297657314311</v>
+        <v>-31.09946487792207</v>
       </c>
       <c r="F93">
-        <v>-2.403066646644581</v>
+        <v>-2.871084288817468</v>
       </c>
       <c r="G93">
-        <v>-3.241515194354638</v>
+        <v>-6.98615270691722</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.127850187975719</v>
       </c>
       <c r="E94">
-        <v>-31.99312752401776</v>
+        <v>-33.53777415837509</v>
       </c>
       <c r="F94">
-        <v>-3.231420795565642</v>
+        <v>-3.534816155412781</v>
       </c>
       <c r="G94">
-        <v>-2.798173556826519</v>
+        <v>-6.887246848385955</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.738862266075021</v>
       </c>
       <c r="E95">
-        <v>-33.84434505598336</v>
+        <v>-34.93538124170337</v>
       </c>
       <c r="F95">
-        <v>-1.975634865371856</v>
+        <v>-3.178368005253348</v>
       </c>
       <c r="G95">
-        <v>-4.277163087041462</v>
+        <v>-7.421929747888105</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.256889765079718</v>
       </c>
       <c r="E96">
-        <v>-36.28932477864969</v>
+        <v>-36.73366544099331</v>
       </c>
       <c r="F96">
-        <v>-3.161196777360717</v>
+        <v>-3.426115299715221</v>
       </c>
       <c r="G96">
-        <v>-3.760406791634465</v>
+        <v>-7.420526076579454</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.700188995000008</v>
       </c>
       <c r="E97">
-        <v>-36.91868303928769</v>
+        <v>-38.55562903086936</v>
       </c>
       <c r="F97">
-        <v>-3.603382610444704</v>
+        <v>-3.770060072296798</v>
       </c>
       <c r="G97">
-        <v>-4.477146521977756</v>
+        <v>-7.606482730065856</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.074551112601682</v>
       </c>
       <c r="E98">
-        <v>-38.76041115397022</v>
+        <v>-41.4303586726266</v>
       </c>
       <c r="F98">
-        <v>-3.466310999568664</v>
+        <v>-3.758682446019347</v>
       </c>
       <c r="G98">
-        <v>-4.163270388853915</v>
+        <v>-8.175568818812112</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.421812135685002</v>
       </c>
       <c r="E99">
-        <v>-39.85460821454758</v>
+        <v>-43.42060035662768</v>
       </c>
       <c r="F99">
-        <v>-3.934239178062049</v>
+        <v>-4.026288192228533</v>
       </c>
       <c r="G99">
-        <v>-4.544727998616438</v>
+        <v>-8.186245328176261</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.7356720272378885</v>
       </c>
       <c r="E100">
-        <v>-44.74664622944974</v>
+        <v>-45.11620820050472</v>
       </c>
       <c r="F100">
-        <v>-3.077767754387764</v>
+        <v>-4.296433712894702</v>
       </c>
       <c r="G100">
-        <v>-5.566633816769746</v>
+        <v>-8.936438121193888</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.09003208827457697</v>
       </c>
       <c r="E101">
-        <v>-45.569793742535</v>
+        <v>-47.05023114393757</v>
       </c>
       <c r="F101">
-        <v>-4.057556576582006</v>
+        <v>-4.232517712462095</v>
       </c>
       <c r="G101">
-        <v>-4.827028148386709</v>
+        <v>-8.505160111610872</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.5645607156752844</v>
       </c>
       <c r="E102">
-        <v>-46.91016091440632</v>
+        <v>-49.95788505596757</v>
       </c>
       <c r="F102">
-        <v>-3.692862857295107</v>
+        <v>-4.382990651180625</v>
       </c>
       <c r="G102">
-        <v>-6.421631860469619</v>
+        <v>-8.588125693370548</v>
       </c>
     </row>
   </sheetData>
